--- a/data/gravel/Revel R+ V4 2025.xlsx
+++ b/data/gravel/Revel R+ V4 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FF9B8A-3AF8-424E-B964-FC4DB709B3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75B545A-8547-6B4C-B56F-B5A907C68923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6260" yWindow="1500" windowWidth="21600" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -338,6 +338,12 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Carbondale, Colorado, USA</t>
   </si>
 </sst>
 </file>
@@ -677,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1511,6 +1517,14 @@
         <v>102</v>
       </c>
     </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>106</v>
+      </c>
+      <c r="B73" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Revel R+ V4 2025.xlsx
+++ b/data/gravel/Revel R+ V4 2025.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75B545A-8547-6B4C-B56F-B5A907C68923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380C37EB-32CB-814F-BFAC-96926C22EE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6260" yWindow="1500" windowWidth="21600" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2000" yWindow="1540" windowWidth="26700" windowHeight="14640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -28,9 +41,6 @@
     <t>model</t>
   </si>
   <si>
-    <t xml:space="preserve">R+ V4 </t>
-  </si>
-  <si>
     <t>model_year</t>
   </si>
   <si>
@@ -43,9 +53,6 @@
     <t>data_range</t>
   </si>
   <si>
-    <t>a8:g32</t>
-  </si>
-  <si>
     <t>frame_size</t>
   </si>
   <si>
@@ -70,87 +77,45 @@
     <t>top_tube_effective_length</t>
   </si>
   <si>
-    <t>Effective Top Tube Length</t>
-  </si>
-  <si>
     <t>seat_tube_length</t>
   </si>
   <si>
-    <t>Seat Tube Length</t>
-  </si>
-  <si>
     <t>seat_tube_angle</t>
   </si>
   <si>
-    <t>Seat Tube Angle</t>
-  </si>
-  <si>
     <t>chainstay_length</t>
   </si>
   <si>
-    <t>Chainstay Length</t>
-  </si>
-  <si>
     <t>bottom_bracket_drop</t>
   </si>
   <si>
-    <t>Bottom Bracket Drop</t>
-  </si>
-  <si>
     <t>bottom_bracket_height</t>
   </si>
   <si>
-    <t>Bottom Bracket Height</t>
-  </si>
-  <si>
     <t>head_tube_angle</t>
   </si>
   <si>
-    <t>Head Tube Angle</t>
-  </si>
-  <si>
     <t>wheelbase</t>
   </si>
   <si>
-    <t>Wheelbase</t>
-  </si>
-  <si>
     <t>head_tube_length</t>
   </si>
   <si>
-    <t>Head Tube Length</t>
-  </si>
-  <si>
     <t>axle_crown</t>
   </si>
   <si>
-    <t>Axle to Crown</t>
-  </si>
-  <si>
     <t>fork_offset_rake</t>
   </si>
   <si>
-    <t>Fork Offset</t>
-  </si>
-  <si>
     <t>trail</t>
   </si>
   <si>
-    <t>Trail</t>
-  </si>
-  <si>
     <t>stack</t>
   </si>
   <si>
-    <t>Stack</t>
-  </si>
-  <si>
     <t>reach</t>
   </si>
   <si>
-    <t>Reach</t>
-  </si>
-  <si>
     <t>standover</t>
   </si>
   <si>
@@ -344,6 +309,105 @@
   </si>
   <si>
     <t>Carbondale, Colorado, USA</t>
+  </si>
+  <si>
+    <t>R+</t>
+  </si>
+  <si>
+    <t>RIDER HEIGHT (in.)</t>
+  </si>
+  <si>
+    <t>5'1"-5'6"</t>
+  </si>
+  <si>
+    <t>5'5"-5'10"</t>
+  </si>
+  <si>
+    <t>5'9"-6'1"</t>
+  </si>
+  <si>
+    <t>6'0"-6'4"</t>
+  </si>
+  <si>
+    <t>6'3"-6'8"</t>
+  </si>
+  <si>
+    <t>RIDER HEIGHT (cm)</t>
+  </si>
+  <si>
+    <t>155 -168cm</t>
+  </si>
+  <si>
+    <t>165 - 178cm</t>
+  </si>
+  <si>
+    <t>175 - 185cm</t>
+  </si>
+  <si>
+    <t>183 - 193cm</t>
+  </si>
+  <si>
+    <t>190 - 203cm</t>
+  </si>
+  <si>
+    <t>EFFECTIVE TOP TUBE LENGTH</t>
+  </si>
+  <si>
+    <t>SEAT TUBE LENGTH</t>
+  </si>
+  <si>
+    <t>SEAT TUBE ANGLE (EFFECTIVE/ACTUAL)</t>
+  </si>
+  <si>
+    <t>CHAIN STAY LENGTH</t>
+  </si>
+  <si>
+    <t>BOTTOM BRACKET DROP</t>
+  </si>
+  <si>
+    <t>BOTTOM BRACKET HEIGHT</t>
+  </si>
+  <si>
+    <t>HEAD TUBE ANGLE</t>
+  </si>
+  <si>
+    <t>WHEEL BASE</t>
+  </si>
+  <si>
+    <t>HEAD TUBE LENGTH</t>
+  </si>
+  <si>
+    <t>AXLE TO CROWN</t>
+  </si>
+  <si>
+    <t>FORK OFFSET</t>
+  </si>
+  <si>
+    <t>TRAIL</t>
+  </si>
+  <si>
+    <t>STACK</t>
+  </si>
+  <si>
+    <t>REACH</t>
+  </si>
+  <si>
+    <t>STANDOVER</t>
+  </si>
+  <si>
+    <t>75/73</t>
+  </si>
+  <si>
+    <t>SEAT TUBE ANGLE (EFFECTIVE)</t>
+  </si>
+  <si>
+    <t>SEAT TUBE ANGLE (ACTUAL)</t>
+  </si>
+  <si>
+    <t>seat_tube_angle_actual</t>
+  </si>
+  <si>
+    <t>a8:g33</t>
   </si>
 </sst>
 </file>
@@ -683,97 +747,97 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
       </c>
       <c r="B3">
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2">
         <v>45943</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B7" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="C8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" t="s">
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="C9">
         <v>540</v>
@@ -791,12 +855,12 @@
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="C10">
         <v>450</v>
@@ -814,593 +878,689 @@
         <v>580</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11">
+        <f>VALUE(LEFT(I11,2))</f>
+        <v>75</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ref="D11:G11" si="0">VALUE(LEFT(J11,2))</f>
+        <v>75</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="H11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" t="s">
+        <v>120</v>
+      </c>
+      <c r="J11" t="s">
+        <v>120</v>
+      </c>
+      <c r="K11" t="s">
+        <v>120</v>
+      </c>
+      <c r="L11" t="s">
+        <v>120</v>
+      </c>
+      <c r="M11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12">
+        <f>VALUE(RIGHT(I11,2))</f>
+        <v>73</v>
+      </c>
+      <c r="D12">
+        <f t="shared" ref="D12:G12" si="1">VALUE(RIGHT(J11,2))</f>
+        <v>73</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13">
+        <v>420</v>
+      </c>
+      <c r="D13">
+        <v>420</v>
+      </c>
+      <c r="E13">
+        <v>420</v>
+      </c>
+      <c r="F13">
+        <v>420</v>
+      </c>
+      <c r="G13">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14">
+        <v>70</v>
+      </c>
+      <c r="D14">
+        <v>70</v>
+      </c>
+      <c r="E14">
+        <v>70</v>
+      </c>
+      <c r="F14">
+        <v>70</v>
+      </c>
+      <c r="G14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15">
+        <v>285</v>
+      </c>
+      <c r="D15">
+        <v>285</v>
+      </c>
+      <c r="E15">
+        <v>285</v>
+      </c>
+      <c r="F15">
+        <v>285</v>
+      </c>
+      <c r="G15">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>19</v>
       </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11">
-        <v>73</v>
-      </c>
-      <c r="D11">
-        <v>73</v>
-      </c>
-      <c r="E11">
-        <v>73</v>
-      </c>
-      <c r="F11">
-        <v>73</v>
-      </c>
-      <c r="G11">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12">
-        <v>420</v>
-      </c>
-      <c r="D12">
-        <v>420</v>
-      </c>
-      <c r="E12">
-        <v>420</v>
-      </c>
-      <c r="F12">
-        <v>420</v>
-      </c>
-      <c r="G12">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13">
-        <v>70</v>
-      </c>
-      <c r="D13">
-        <v>70</v>
-      </c>
-      <c r="E13">
-        <v>70</v>
-      </c>
-      <c r="F13">
-        <v>70</v>
-      </c>
-      <c r="G13">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14">
-        <v>285</v>
-      </c>
-      <c r="D14">
-        <v>285</v>
-      </c>
-      <c r="E14">
-        <v>285</v>
-      </c>
-      <c r="F14">
-        <v>285</v>
-      </c>
-      <c r="G14">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15">
+      <c r="B16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16">
         <v>71.5</v>
       </c>
-      <c r="D15">
+      <c r="D16">
         <v>71.5</v>
       </c>
-      <c r="E15">
+      <c r="E16">
         <v>71.5</v>
       </c>
-      <c r="F15">
+      <c r="F16">
         <v>71.5</v>
       </c>
-      <c r="G15">
+      <c r="G16">
         <v>71.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16">
-        <v>1016</v>
-      </c>
-      <c r="D16">
-        <v>1034</v>
-      </c>
-      <c r="E16">
-        <v>1049</v>
-      </c>
-      <c r="F16">
-        <v>1064</v>
-      </c>
-      <c r="G16">
-        <v>1082</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C17">
-        <v>110</v>
+        <v>1016</v>
       </c>
       <c r="D17">
-        <v>136</v>
+        <v>1034</v>
       </c>
       <c r="E17">
-        <v>157</v>
+        <v>1049</v>
       </c>
       <c r="F17">
-        <v>178</v>
+        <v>1064</v>
       </c>
       <c r="G17">
-        <v>205</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="C18">
-        <v>395</v>
+        <v>110</v>
       </c>
       <c r="D18">
-        <v>395</v>
+        <v>136</v>
       </c>
       <c r="E18">
-        <v>395</v>
+        <v>157</v>
       </c>
       <c r="F18">
-        <v>395</v>
+        <v>178</v>
       </c>
       <c r="G18">
-        <v>395</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="C19">
-        <v>47</v>
+        <v>395</v>
       </c>
       <c r="D19">
-        <v>47</v>
+        <v>395</v>
       </c>
       <c r="E19">
-        <v>47</v>
+        <v>395</v>
       </c>
       <c r="F19">
-        <v>47</v>
+        <v>395</v>
       </c>
       <c r="G19">
-        <v>47</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="C20">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D20">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="E20">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="F20">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="G20">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="C21">
-        <v>535</v>
+        <v>69</v>
       </c>
       <c r="D21">
-        <v>560</v>
+        <v>69</v>
       </c>
       <c r="E21">
-        <v>580</v>
+        <v>69</v>
       </c>
       <c r="F21">
-        <v>600</v>
+        <v>69</v>
       </c>
       <c r="G21">
-        <v>625</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="C22">
-        <v>397</v>
+        <v>535</v>
       </c>
       <c r="D22">
-        <v>407</v>
+        <v>560</v>
       </c>
       <c r="E22">
-        <v>415</v>
+        <v>580</v>
       </c>
       <c r="F22">
-        <v>423</v>
+        <v>600</v>
       </c>
       <c r="G22">
-        <v>433</v>
+        <v>625</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>118</v>
+      </c>
+      <c r="C23">
+        <v>397</v>
+      </c>
+      <c r="D23">
+        <v>407</v>
+      </c>
+      <c r="E23">
+        <v>415</v>
+      </c>
+      <c r="F23">
+        <v>423</v>
+      </c>
+      <c r="G23">
+        <v>433</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>119</v>
+      </c>
+      <c r="C24">
+        <v>720</v>
+      </c>
+      <c r="D24">
+        <v>760</v>
+      </c>
+      <c r="E24">
+        <v>775</v>
+      </c>
+      <c r="F24">
+        <v>795</v>
+      </c>
+      <c r="G24">
+        <v>823</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28">
-        <v>700</v>
-      </c>
-      <c r="D28">
-        <v>700</v>
-      </c>
-      <c r="E28">
-        <v>700</v>
-      </c>
-      <c r="F28">
-        <v>700</v>
-      </c>
-      <c r="G28">
-        <v>700</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C29">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="D29">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="E29">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="F29">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="G29">
-        <v>50</v>
+        <v>700</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30">
         <v>50</v>
       </c>
-      <c r="B30" t="s">
+      <c r="D30">
         <v>50</v>
       </c>
-      <c r="C30">
-        <v>40</v>
-      </c>
-      <c r="D30">
-        <v>40</v>
-      </c>
       <c r="E30">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F30">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G30">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C31">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D31">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="E31">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="F31">
-        <v>183</v>
+        <v>40</v>
       </c>
       <c r="G31">
-        <v>190</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C32">
+        <v>155</v>
+      </c>
+      <c r="D32">
+        <v>165</v>
+      </c>
+      <c r="E32">
+        <v>175</v>
+      </c>
+      <c r="F32">
+        <v>183</v>
+      </c>
+      <c r="G32">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33">
         <v>168</v>
       </c>
-      <c r="D32">
+      <c r="D33">
         <v>178</v>
       </c>
-      <c r="E32">
+      <c r="E33">
         <v>185</v>
       </c>
-      <c r="F32">
+      <c r="F33">
         <v>193</v>
       </c>
-      <c r="G32">
+      <c r="G33">
         <v>203</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" t="s">
+        <v>95</v>
+      </c>
+      <c r="E34" t="s">
+        <v>96</v>
+      </c>
+      <c r="F34" t="s">
+        <v>97</v>
+      </c>
+      <c r="G34" t="s">
+        <v>98</v>
+      </c>
+      <c r="H34" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" t="s">
+        <v>101</v>
+      </c>
+      <c r="E35" t="s">
+        <v>102</v>
+      </c>
+      <c r="F35" t="s">
+        <v>103</v>
+      </c>
+      <c r="G35" t="s">
+        <v>104</v>
+      </c>
+      <c r="H35" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>60</v>
-      </c>
-      <c r="B42">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43">
         <v>2.1</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>61</v>
-      </c>
-      <c r="B43" s="1"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="B44" s="1"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48">
         <v>142</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>66</v>
-      </c>
-      <c r="B48">
-        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>67</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>104</v>
+        <v>50</v>
+      </c>
+      <c r="B49">
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>68</v>
+        <v>51</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>69</v>
-      </c>
-      <c r="B51">
-        <v>27.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>70</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>105</v>
+        <v>53</v>
+      </c>
+      <c r="B52">
+        <v>27.2</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>71</v>
-      </c>
-      <c r="B53">
-        <v>50</v>
+        <v>54</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>55</v>
+      </c>
+      <c r="B54">
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>73</v>
-      </c>
-      <c r="B55">
-        <v>160</v>
+        <v>56</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B56">
         <v>160</v>
@@ -1408,121 +1568,129 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>58</v>
+      </c>
+      <c r="B57">
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>76</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>61</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>80</v>
-      </c>
-      <c r="B62">
-        <v>3</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>65</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>83</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>66</v>
+      </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>84</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>101</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>87</v>
-      </c>
-      <c r="B69">
-        <v>2799</v>
+        <v>70</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B70">
-        <v>4499</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>72</v>
+      </c>
+      <c r="B71">
+        <v>4499</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>90</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>106</v>
-      </c>
-      <c r="B73" t="s">
-        <v>107</v>
+        <v>74</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B74" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Revel R+ V4 2025.xlsx
+++ b/data/gravel/Revel R+ V4 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380C37EB-32CB-814F-BFAC-96926C22EE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA026A3-3A52-CA48-B51E-A3F50BA39436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2000" yWindow="1540" windowWidth="26700" windowHeight="14640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="131">
   <si>
     <t>brand</t>
   </si>
@@ -408,6 +408,24 @@
   </si>
   <si>
     <t>a8:g33</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -747,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1518,178 +1536,208 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52">
-        <v>27.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54">
-        <v>50</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>57</v>
-      </c>
-      <c r="B56">
-        <v>160</v>
+        <v>51</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>58</v>
-      </c>
-      <c r="B57">
-        <v>160</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B58">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>61</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>87</v>
+        <v>55</v>
+      </c>
+      <c r="B60">
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="B62">
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>65</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>67</v>
-      </c>
-      <c r="B66" s="1"/>
+        <v>61</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>68</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>69</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>70</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>85</v>
+        <v>64</v>
+      </c>
+      <c r="B69">
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B70">
-        <v>2799</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>72</v>
-      </c>
-      <c r="B71">
-        <v>4499</v>
+        <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>73</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B72" s="1"/>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>69</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>70</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>71</v>
+      </c>
+      <c r="B76">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>72</v>
+      </c>
+      <c r="B77">
+        <v>4499</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>74</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>90</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>91</v>
       </c>
     </row>
